--- a/Retail Sales Dashboard in Excel.xlsx
+++ b/Retail Sales Dashboard in Excel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ba21cf4e631f4a67/Desktop/Excel Projects/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ba21cf4e631f4a67/Desktop/Excel Projects/Retail Sales Excel Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{4958AFA2-BE18-4710-8F94-F179EBDA8E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDA90DB4-0F3E-40B2-B3F5-A4705FAA21D4}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{4958AFA2-BE18-4710-8F94-F179EBDA8E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41AF1B20-96FB-4F1F-8E9D-5994BFF006A9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FD3357F1-5F0B-4BB7-9814-1D5A1194D8F6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{FD3357F1-5F0B-4BB7-9814-1D5A1194D8F6}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Raw_Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -22288,7 +22288,366 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE7E8DD0-E470-4C9F-A953-870DF1B5885B}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70D87914-3D46-4153-AC48-C03490135378}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="F11:G15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Amount" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{54FC0734-2360-4DB7-9F73-D5F30AE7153B}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="F18:G22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" countASubtotal="1">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="countA"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="9"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Transaction ID" fld="0" subtotal="count" baseField="9" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E737B04F-8071-4D8A-B5C3-1FC37475CCA7}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="I11:M16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="5"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Amount" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{506A8282-F5A1-434A-A0D7-2FACB1EBD1BD}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="B11:C15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="11">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="22" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Amount" fld="8" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BE7E8DD0-E470-4C9F-A953-870DF1B5885B}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="B18:C21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="11">
     <pivotField showAll="0"/>
@@ -22380,365 +22739,6 @@
           </reference>
           <reference field="3" count="1" selected="0">
             <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{70D87914-3D46-4153-AC48-C03490135378}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
-  <location ref="F11:G15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Amount" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{54FC0734-2360-4DB7-9F73-D5F30AE7153B}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="F18:G22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" countASubtotal="1">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="countA"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="9"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Transaction ID" fld="0" subtotal="count" baseField="9" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E737B04F-8071-4D8A-B5C3-1FC37475CCA7}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" showDrill="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="I11:M16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="5"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Amount" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{506A8282-F5A1-434A-A0D7-2FACB1EBD1BD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="B11:C15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="11">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="22" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Amount" fld="8" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="4" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
@@ -89322,11 +89322,11 @@
   <dimension ref="B3:M22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.5546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
@@ -89413,7 +89413,7 @@
       <c r="B12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="9">
         <v>143515</v>
       </c>
       <c r="F12" s="7" t="s">
@@ -89442,7 +89442,7 @@
       <c r="B13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="9">
         <v>155580</v>
       </c>
       <c r="F13" s="7" t="s">
@@ -89471,7 +89471,7 @@
       <c r="B14" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="9">
         <v>156905</v>
       </c>
       <c r="F14" s="7" t="s">
@@ -89500,7 +89500,7 @@
       <c r="B15" s="7" t="s">
         <v>1022</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="9">
         <v>456000</v>
       </c>
       <c r="F15" s="7" t="s">
@@ -89621,6 +89621,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D801453-5FE7-4923-AC63-99A7AD1E33E1}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="E1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -89657,11 +89660,12 @@
     <mergeCell ref="E1:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="67" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
   </extLst>
